--- a/tests/integration_workspace/dashboard_full_pipeline/output/price_change_report.xlsx
+++ b/tests/integration_workspace/dashboard_full_pipeline/output/price_change_report.xlsx
@@ -489,6 +489,11 @@
           <t>SKU-APPLE</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SVO shampoo apple 1 l</t>
+        </is>
+      </c>
       <c r="D2" t="n">
         <v>35.5</v>
       </c>
@@ -497,12 +502,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-05T18:55:03.233973+00:00</t>
+          <t>2026-08-06T16:37:00.557317+00:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-05T18:55:03.233973+00:00</t>
+          <t>2026-08-06T16:37:00.557317+00:00</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -522,6 +527,11 @@
           <t>SKU-LIME</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SVO shampoo lime 1 l</t>
+        </is>
+      </c>
       <c r="D3" t="n">
         <v>39</v>
       </c>
@@ -530,12 +540,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-05T18:55:03.233973+00:00</t>
+          <t>2026-08-06T16:37:00.557317+00:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-05T18:55:03.233973+00:00</t>
+          <t>2026-08-06T16:37:00.557317+00:00</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">

--- a/tests/integration_workspace/dashboard_full_pipeline/output/price_change_report.xlsx
+++ b/tests/integration_workspace/dashboard_full_pipeline/output/price_change_report.xlsx
@@ -502,12 +502,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-06T16:37:00.557317+00:00</t>
+          <t>2026-09-03T09:07:46.189545+00:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-06T16:37:00.557317+00:00</t>
+          <t>2026-09-03T09:07:46.189545+00:00</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -540,12 +540,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-06T16:37:00.557317+00:00</t>
+          <t>2026-09-03T09:07:46.189545+00:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-06T16:37:00.557317+00:00</t>
+          <t>2026-09-03T09:07:46.189545+00:00</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
